--- a/docs/指标结果模板.xlsx
+++ b/docs/指标结果模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leefa\Desktop\浦发\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A92266-E633-4304-9BE5-A620BDCF4032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE5F4E14-1289-4946-B55C-94BC07BAE96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6BBC0181-4A95-4707-9ABD-C73491E425E9}"/>
   </bookViews>
@@ -36,17 +36,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>指标数值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础维度（EMP/ORG/CUST；NULL=不区分维度）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -61,16 +57,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ORG</t>
-  </si>
-  <si>
-    <t>基础性存款月均余额</t>
-  </si>
-  <si>
-    <t>基础性存款年日均余额</t>
-  </si>
-  <si>
     <t>指标名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础维度（EMP/ORG/CUST）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XXXXX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -81,7 +76,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +98,22 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -161,13 +172,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -509,7 +520,7 @@
   <cols>
     <col min="2" max="2" width="21.6640625" customWidth="1"/>
     <col min="3" max="3" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -518,58 +529,49 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2812931</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5">
-        <v>59287123.909999996</v>
+      <c r="D2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4">
-        <v>610444991</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="5">
-        <v>659287123.90999997</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="EMP=员工号_x000a_ORG=机构号_x000a_CUST=客户编号" sqref="B1:B1048576" xr:uid="{F6363DAD-FB21-4B27-98EA-CAD25339466F}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="EMP=员工号_x000a_ORG=机构号_x000a_CUST=客户编号" sqref="B2:B1048576" xr:uid="{F6363DAD-FB21-4B27-98EA-CAD25339466F}">
       <formula1>"EMP,ORG,CUST"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showErrorMessage="1" prompt="EMP=员工号_x000a_ORG=机构号_x000a_CUST=客户编号" sqref="B1" xr:uid="{595DB0DA-271F-4EF6-9CC1-B2F3691B6A33}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
